--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206000</v>
+        <v>196000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>360706.8965517241</v>
+        <v>360599.6168582375</v>
       </c>
       <c r="H9" t="n">
-        <v>-30000</v>
+        <v>-63000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1271186440677966</v>
+        <v>-0.2432432432432433</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -563,21 +563,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>11.164138</v>
+        <v>11.111439</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Jan 2026</t>
+          <t>Apr 2026</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11.07203170731707</v>
+        <v>11.05600841463415</v>
       </c>
       <c r="H4" t="n">
-        <v>0.05875699999999995</v>
+        <v>-0.01280799999999971</v>
       </c>
       <c r="I4" t="n">
-        <v>0.005290858548662126</v>
+        <v>-0.001151358829051504</v>
       </c>
     </row>
     <row r="5">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>196000</v>
+        <v>197000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>360599.6168582375</v>
+        <v>360503.8314176245</v>
       </c>
       <c r="H9" t="n">
-        <v>-63000</v>
+        <v>-36000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2432432432432433</v>
+        <v>-0.1545064377682404</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -680,21 +680,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>7.271</v>
+        <v>7.079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>7.839611570247935</v>
+        <v>7.849371900826446</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1819999999999995</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02567357878403153</v>
+        <v>0.02312472900708197</v>
       </c>
     </row>
     <row r="8">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>360503.8314176245</v>
+        <v>360409.9616858237</v>
       </c>
       <c r="H9" t="n">
-        <v>-36000</v>
+        <v>-22000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1545064377682404</v>
+        <v>-0.1004566210045662</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -719,21 +719,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aug 2026</t>
+          <t>Sep 2026</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4.543333333333332</v>
+        <v>4.537499999999999</v>
       </c>
       <c r="H8" t="n">
         <v>-0.2000000000000002</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.04651162790697679</v>
+        <v>-0.04545454545454549</v>
       </c>
     </row>
     <row r="9">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -641,21 +641,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1357221.44</v>
+        <v>1352414</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jul 2026</t>
+          <t>Aug 2026</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1125650.468347108</v>
+        <v>1129051.290165289</v>
       </c>
       <c r="H6" t="n">
-        <v>46939.96999999997</v>
+        <v>44102.34000000008</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03582434085708315</v>
+        <v>0.0337093533202938</v>
       </c>
     </row>
     <row r="7">

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -762,17 +762,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sep 2026</t>
+          <t>Oct 2026</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>360409.9616858237</v>
+        <v>360321.8390804598</v>
       </c>
       <c r="H9" t="n">
-        <v>-22000</v>
+        <v>-28000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1004566210045662</v>
+        <v>-0.1244444444444444</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>197000</v>
+        <v>199000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>360321.8390804598</v>
+        <v>360226.0536398467</v>
       </c>
       <c r="H9" t="n">
-        <v>-28000</v>
+        <v>-34000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1244444444444444</v>
+        <v>-0.1459227467811159</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -758,7 +758,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>199000</v>
+        <v>194000</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>360226.0536398467</v>
+        <v>360095.7854406131</v>
       </c>
       <c r="H9" t="n">
-        <v>-34000</v>
+        <v>-28000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1459227467811159</v>
+        <v>-0.1261261261261261</v>
       </c>
     </row>
   </sheetData>

--- a/macro_credit_metrics.xlsx
+++ b/macro_credit_metrics.xlsx
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>360095.7854406131</v>
+        <v>359978.9272030651</v>
       </c>
       <c r="H9" t="n">
-        <v>-28000</v>
+        <v>-37000</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1261261261261261</v>
+        <v>-0.1601731601731602</v>
       </c>
     </row>
   </sheetData>
